--- a/assets/excel/donation_template.xlsx
+++ b/assets/excel/donation_template.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sản Phẩm" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DanhMuc" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="DonVi" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="TinhTrang" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
-        <bgColor rgb="0000B050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -136,6 +122,24 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I2" headerRowCount="1">
+  <autoFilter ref="A1:I2"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên Vật Phẩm"/>
+    <tableColumn id="3" name="Danh Mục"/>
+    <tableColumn id="4" name="Mô Tả Chi Tiết"/>
+    <tableColumn id="5" name="Số Lượng"/>
+    <tableColumn id="6" name="Đơn Vị"/>
+    <tableColumn id="7" name="Tình Trạng"/>
+    <tableColumn id="8" name="Giá Trị Ước Tính (vnd)"/>
+    <tableColumn id="9" name="Hình ảnh (URL)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,288 +431,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Tên Vật Phẩm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Danh Mục</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Mô Tả Chi Tiết</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Số Lượng</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Đơn Vị</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Tình Trạng</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Giá Trị Ước Tính (vnd)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Hình ảnh (URL)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
+      <c r="A2">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quần áo cũ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quần áo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Áo sơ mi nam size L</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tốt</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Lỗi" error="Vui lòng chọn danh mục từ danh sách" promptTitle="Danh Mục" prompt="Chọn danh mục" type="list">
-      <formula1>DanhMuc!$A$1:$A$8</formula1>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Quần áo,Điện tử,Sách,Gia dụng,Đồ chơi,Thực phẩm,Y tế,Khác,Điện lạnh,Đồ gia dụng,Nhà bếp,Vệ sinh"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Lỗi" error="Vui lòng chọn đơn vị từ danh sách" promptTitle="Đơn Vị" prompt="Chọn đơn vị" type="list">
-      <formula1>DonVi!$A$1:$A$12</formula1>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cái,bộ,kg,cuốn,thùng"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Lỗi" error="Vui lòng chọn tình trạng từ danh sách" promptTitle="Tình Trạng" prompt="Chọn tình trạng" type="list">
-      <formula1>TinhTrang!$A$1:$A$4</formula1>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Mới,Như mới,Tốt,Khá,Cũ"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Điện tử</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Đồ chơi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gia dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Quần áo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Thực phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Y tế</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chiếc</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hộp</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Đôi</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gói</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Chai</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lọ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thùng</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Tốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cần sửa</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hỏng</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>